--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.7029290326668</v>
+        <v>12.95172596780836</v>
       </c>
       <c r="D2" t="n">
-        <v>80.8802727261741</v>
+        <v>13.14304431800329</v>
       </c>
       <c r="E2" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F2" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.16604193832059</v>
+        <v>6.689481814977096</v>
       </c>
       <c r="D3" t="n">
-        <v>40.11812911706373</v>
+        <v>6.519195981522857</v>
       </c>
       <c r="E3" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F3" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.08556701870783</v>
+        <v>10.73890464054002</v>
       </c>
       <c r="D4" t="n">
-        <v>66.99183017680917</v>
+        <v>10.88617240373149</v>
       </c>
       <c r="E4" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F4" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.08681998878374</v>
+        <v>10.25160824817736</v>
       </c>
       <c r="D5" t="n">
-        <v>64.25599821757316</v>
+        <v>10.44159971035564</v>
       </c>
       <c r="E5" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F5" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.77729615297223</v>
+        <v>8.088810624857988</v>
       </c>
       <c r="D6" t="n">
-        <v>49.01300370778848</v>
+        <v>7.964613102515628</v>
       </c>
       <c r="E6" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F6" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.97920435250448</v>
+        <v>8.771620707281979</v>
       </c>
       <c r="D7" t="n">
-        <v>54.6220160822877</v>
+        <v>8.876077613371752</v>
       </c>
       <c r="E7" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F7" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.137957274887206</v>
+        <v>1.322418057169171</v>
       </c>
       <c r="D8" t="n">
-        <v>9.196632375885098</v>
+        <v>1.494452761081329</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F8" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.439464914302</v>
+        <v>3.646413048574076</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1447028895891</v>
+        <v>3.761014219558229</v>
       </c>
       <c r="E9" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F9" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.92285383327742</v>
+        <v>4.04996374790758</v>
       </c>
       <c r="D10" t="n">
-        <v>26.13096192003199</v>
+        <v>4.246281312005197</v>
       </c>
       <c r="E10" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F10" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.0760019609631</v>
+        <v>3.099850318656504</v>
       </c>
       <c r="D11" t="n">
-        <v>20.21273526993917</v>
+        <v>3.284569481365115</v>
       </c>
       <c r="E11" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F11" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.70589709008834</v>
+        <v>5.477208277139356</v>
       </c>
       <c r="D12" t="n">
-        <v>15.4434452114805</v>
+        <v>2.509559846865582</v>
       </c>
       <c r="E12" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F12" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.02501323708417</v>
+        <v>3.741564651026178</v>
       </c>
       <c r="D13" t="n">
-        <v>23.01779504837266</v>
+        <v>3.740391695360558</v>
       </c>
       <c r="E13" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F13" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.99361209025243</v>
+        <v>5.523961964666021</v>
       </c>
       <c r="D14" t="n">
-        <v>19.19513074106231</v>
+        <v>3.119208745422626</v>
       </c>
       <c r="E14" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F14" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.36099674676031</v>
+        <v>4.933661971348551</v>
       </c>
       <c r="D15" t="n">
-        <v>23.76783873244265</v>
+        <v>3.862273794021931</v>
       </c>
       <c r="E15" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F15" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>48.43593834599253</v>
+        <v>7.870839981223787</v>
       </c>
       <c r="D16" t="n">
-        <v>7.525485027287789</v>
+        <v>1.222891316934266</v>
       </c>
       <c r="E16" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F16" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>67.38220425139286</v>
+        <v>10.94960819085134</v>
       </c>
       <c r="D17" t="n">
-        <v>34.3991009111233</v>
+        <v>5.589853898057537</v>
       </c>
       <c r="E17" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F17" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>60.47340561689913</v>
+        <v>9.826928412746108</v>
       </c>
       <c r="D18" t="n">
-        <v>55.52026656996524</v>
+        <v>9.022043317619353</v>
       </c>
       <c r="E18" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F18" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>73.33033880301048</v>
+        <v>11.9161800554892</v>
       </c>
       <c r="D19" t="n">
-        <v>46.23131460331189</v>
+        <v>7.512588623038182</v>
       </c>
       <c r="E19" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F19" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>61.39381224262991</v>
+        <v>9.97649448942736</v>
       </c>
       <c r="D20" t="n">
-        <v>60.2166620580604</v>
+        <v>9.785207584434815</v>
       </c>
       <c r="E20" t="n">
-        <v>20.2679276249321</v>
+        <v>3.293538239051466</v>
       </c>
       <c r="F20" t="n">
-        <v>20.99802436122411</v>
+        <v>3.412178958698918</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
